--- a/jogos_2024-12-02.xlsx
+++ b/jogos_2024-12-02.xlsx
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Havadar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="M5" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="O5" t="n">
         <v>3.75</v>
@@ -1074,25 +1074,25 @@
         <v>3.4</v>
       </c>
       <c r="R5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.63</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X5" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="Y5" t="n">
         <v>2.75</v>
@@ -1101,38 +1101,38 @@
         <v>1.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['3', '62', '89']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
         <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45628.375</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,109 +1159,109 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Havadar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['44', '84']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.97</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45628.375</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="M7" t="n">
-        <v>2.35</v>
+        <v>3.13</v>
       </c>
       <c r="N7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X7" t="n">
         <v>3.2</v>
       </c>
-      <c r="O7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="Y7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['44', '84']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45628.375</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="X8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['3', '62', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45628.375</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.95</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.25</v>
+        <v>3.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['23', '41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45628.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="X11" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['30']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45628.5</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,80 +1959,80 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y12" t="n">
         <v>2.63</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.25</v>
-      </c>
       <c r="Z12" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['30']</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['2']</t>
+          <t>['23', '41']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AJ12" t="n">
         <v>2.4</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O20" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="X20" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['18', '22', '70', '79']</t>
+          <t>['52', '58']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45628.625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,19 +3094,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.75</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
@@ -3144,59 +3144,59 @@
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>3.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['21']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['52', '58']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45628.625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="O24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['18', '22', '70', '79']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI24" t="n">
         <v>2.88</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['21']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45628.625</v>
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M28" t="n">
         <v>2.88</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="S28" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="T28" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X28" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['15', '50', '63', '73', '88']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['86']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45628.6875</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -4152,55 +4152,55 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA29" t="n">
         <v>4.33</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AB29" t="n">
         <v>1.2</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.13</v>
       </c>
       <c r="AC29" t="n">
         <v>2.38</v>
@@ -4210,25 +4210,25 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45628.6875</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="O30" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="P30" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="X30" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA30" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['13', '17', '84']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45628.6875</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X31" t="n">
         <v>2.8</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="Y31" t="n">
         <v>2.25</v>
       </c>
-      <c r="O31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S31" t="n">
+      <c r="Z31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['13', '17', '84']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45628.6875</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,19 +4513,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>SPAL</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>2.88</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['15', '50', '63', '73', '88']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI32" t="n">
         <v>2.2</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>7</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>3.75</v>
+        <v>1.83</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45628.6875</v>
@@ -4761,29 +4761,29 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.7</v>
+        <v>2.14</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="N34" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="O34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
         <v>4.33</v>
       </c>
-      <c r="P34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R34" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="T34" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U34" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V34" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W34" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="X34" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AA34" t="n">
-        <v>4.65</v>
+        <v>4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45628.70833333334</v>
@@ -4890,29 +4890,29 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.14</v>
+        <v>3.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="O35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2.88</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z35" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['72']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45628.70833333334</v>
@@ -5148,35 +5148,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vere United</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="P37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC37" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q37" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="AD37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['13', '43', '61']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI37" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45628.79166666666</v>
@@ -5277,35 +5277,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Vere United</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M38" t="n">
         <v>3.4</v>
       </c>
-      <c r="M38" t="n">
-        <v>3</v>
-      </c>
       <c r="N38" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="O38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q38" t="n">
         <v>4.33</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y38" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA38" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['13', '43', '61']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI38" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45628.79166666666</v>
